--- a/교재/엑셀교재v2/013-014_통계함수_실습.xlsx
+++ b/교재/엑셀교재v2/013-014_통계함수_실습.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142ABA72-DCE9-4134-A26A-68174B78ED6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774809DA-78DA-4C39-96E8-438BE6CB89BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="375" windowWidth="22200" windowHeight="14790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24435" yWindow="810" windowWidth="22200" windowHeight="14790" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="통계_연습" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="44">
   <si>
     <t>서울</t>
   </si>
@@ -54,16 +54,7 @@
     <t>대구</t>
   </si>
   <si>
-    <t>사진 자료: 노트 013~014페이지</t>
-  </si>
-  <si>
-    <t>H2는 제목입니다. 등수는 H3:H9에 입력합니다.</t>
-  </si>
-  <si>
     <t>부산</t>
-  </si>
-  <si>
-    <t>마지막 문제는 013페이지 지시대로 D24에 입력합니다.</t>
   </si>
   <si>
     <t>서울의 개수</t>
@@ -276,11 +267,11 @@
     <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -566,9 +557,7 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
@@ -590,9 +579,7 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
@@ -603,7 +590,7 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1"/>
@@ -612,9 +599,7 @@
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
@@ -660,14 +645,14 @@
     </row>
     <row r="8" spans="1:12" ht="24.95" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>10</v>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="1"/>
@@ -682,14 +667,14 @@
     </row>
     <row r="9" spans="1:12" ht="24.95" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>11</v>
+      <c r="B9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="1"/>
@@ -704,14 +689,14 @@
     </row>
     <row r="10" spans="1:12" ht="24.95" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>12</v>
+      <c r="B10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="1"/>
@@ -724,19 +709,19 @@
     </row>
     <row r="11" spans="1:12" ht="24.95" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>13</v>
+      <c r="B11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="1"/>
@@ -752,7 +737,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="1"/>
@@ -768,7 +753,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="1"/>
@@ -784,7 +769,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="1"/>
@@ -822,22 +807,22 @@
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>18</v>
+      <c r="B17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="1"/>
       <c r="G17" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -852,7 +837,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2">
         <v>50</v>
@@ -870,7 +855,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
@@ -888,7 +873,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2">
         <v>60</v>
@@ -906,7 +891,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H21" s="2">
         <v>70</v>
@@ -919,20 +904,20 @@
     <row r="22" spans="1:12" ht="24.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H22" s="2">
         <v>60</v>
@@ -950,7 +935,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H23" s="2">
         <v>40</v>
@@ -964,7 +949,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="1"/>
@@ -998,7 +983,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1024,17 +1009,17 @@
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>26</v>
+      <c r="B28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1061,16 +1046,16 @@
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1085,14 +1070,14 @@
       <c r="B31" s="1">
         <v>100</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="13"/>
+      <c r="C31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="11"/>
       <c r="E31" s="6"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1103,16 +1088,16 @@
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="11"/>
       <c r="E32" s="6"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1125,14 +1110,14 @@
       <c r="B33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="13"/>
+      <c r="C33" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="11"/>
       <c r="E33" s="6"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1143,14 +1128,14 @@
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="13"/>
+      <c r="C34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="11"/>
       <c r="E34" s="6"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1163,14 +1148,14 @@
       <c r="B35" s="1">
         <v>0</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="13"/>
+      <c r="C35" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="11"/>
       <c r="E35" s="6"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1184,14 +1169,14 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="13"/>
+      <c r="C36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="11"/>
       <c r="E36" s="6"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1207,7 +1192,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1223,7 +1208,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1262,7 +1247,7 @@
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -1291,6 +1276,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
@@ -1300,11 +1290,6 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1364,7 +1349,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1388,9 +1373,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
@@ -1415,9 +1398,7 @@
         <v>7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
@@ -1428,7 +1409,7 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1"/>
@@ -1440,9 +1421,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
@@ -1494,14 +1473,14 @@
     </row>
     <row r="8" spans="1:12" ht="24.95" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>10</v>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="E8" s="10">
         <f>COUNTIF(B2:E6,"서울")</f>
@@ -1522,14 +1501,14 @@
     </row>
     <row r="9" spans="1:12" ht="24.95" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>11</v>
+      <c r="B9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="E9" s="10">
         <f>COUNTA(B2:E6)</f>
@@ -1550,14 +1529,14 @@
     </row>
     <row r="10" spans="1:12" ht="24.95" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>12</v>
+      <c r="B10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="E10" s="10">
         <f>COUNTBLANK(B2:E6)</f>
@@ -1573,14 +1552,14 @@
     </row>
     <row r="11" spans="1:12" ht="24.95" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>13</v>
+      <c r="B11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="E11" s="10">
         <f>COUNT(B2:E6)</f>
@@ -1588,7 +1567,7 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H11" s="9">
         <f>_xlfn.VAR.S(G3:G9)</f>
@@ -1607,7 +1586,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H12" s="9">
         <f>_xlfn.STDEV.S(G3:G9)</f>
@@ -1626,7 +1605,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H13" s="10">
         <f>LARGE(G3:G9,2)</f>
@@ -1645,7 +1624,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H14" s="10">
         <f>SMALL(G3:G9,3)</f>
@@ -1686,14 +1665,14 @@
     </row>
     <row r="17" spans="1:12" ht="24.95" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>18</v>
+      <c r="B17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="E17" s="10">
         <f>VALUE(MID(B17,6,4))</f>
@@ -1701,10 +1680,10 @@
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1719,7 +1698,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2">
         <v>50</v>
@@ -1737,7 +1716,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
@@ -1755,7 +1734,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2">
         <v>60</v>
@@ -1773,7 +1752,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H21" s="2">
         <v>70</v>
@@ -1786,20 +1765,20 @@
     <row r="22" spans="1:12" ht="24.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H22" s="2">
         <v>60</v>
@@ -1817,7 +1796,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H23" s="2">
         <v>40</v>
@@ -1831,7 +1810,7 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D24" s="10">
         <f>COUNTIFS(G18:G23,"A",H18:H23,"&gt;=50")</f>
@@ -1868,7 +1847,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1894,17 +1873,17 @@
     </row>
     <row r="28" spans="1:12" ht="24.95" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>26</v>
+      <c r="B28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1931,16 +1910,16 @@
     <row r="30" spans="1:12" ht="24.95" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1955,17 +1934,17 @@
       <c r="B31" s="1">
         <v>100</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="13"/>
+      <c r="C31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="11"/>
       <c r="E31" s="10">
         <f>COUNT(B31:B36)</f>
         <v>2</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1976,19 +1955,19 @@
     <row r="32" spans="1:12" ht="24.95" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="11"/>
       <c r="E32" s="10">
         <f>COUNTA(B31:B36)</f>
         <v>5</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2001,17 +1980,17 @@
       <c r="B33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="13"/>
+      <c r="C33" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="11"/>
       <c r="E33" s="10">
         <f>COUNTBLANK(B31:B36)</f>
         <v>2</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2022,17 +2001,17 @@
     <row r="34" spans="1:12" ht="24.95" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-      <c r="C34" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="13"/>
+      <c r="C34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="11"/>
       <c r="E34" s="10">
         <f>_xlfn.RANK.EQ(G4,$G$3:$G$9,1)</f>
         <v>1</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2045,17 +2024,17 @@
       <c r="B35" s="1">
         <v>0</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="13"/>
+      <c r="C35" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="11"/>
       <c r="E35" s="10">
         <f>LARGE(G3:G9,1)</f>
         <v>600</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2069,17 +2048,17 @@
         <f>""</f>
         <v/>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="13"/>
+      <c r="C36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="11"/>
       <c r="E36" s="10">
         <f>COUNTIF(G3:G9,"&gt;=350")</f>
         <v>5</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2098,7 +2077,7 @@
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2117,7 +2096,7 @@
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2156,7 +2135,7 @@
     <row r="41" spans="1:12" ht="24.95" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -2185,6 +2164,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B17:D17"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
@@ -2194,11 +2178,6 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/교재/엑셀교재v2/013-014_통계함수_실습.xlsx
+++ b/교재/엑셀교재v2/013-014_통계함수_실습.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -272,6 +272,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -513,7 +525,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="24.95" customHeight="1">
+    <row r="2" spans="1:12" ht="44" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2">
         <v>100</v>
@@ -531,12 +543,17 @@
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>2</v>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내림차순 등수
+(RANK.EQ 함수 사용)</t>
+        </is>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>3</v>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -643,10 +660,12 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="24.95" customHeight="1">
+    <row r="8" spans="1:12" ht="44" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="13" t="s">
-        <v>7</v>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울의 개수 (COUNTIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C8" s="13" t="s">
         <v>7</v>
@@ -665,10 +684,12 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="24.95" customHeight="1">
+    <row r="9" spans="1:12" ht="44" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="13" t="s">
-        <v>8</v>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비어 있지 않은 셀의 개수 (COUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C9" s="13" t="s">
         <v>8</v>
@@ -687,10 +708,12 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" ht="24.95" customHeight="1">
+    <row r="10" spans="1:12" ht="44" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="13" t="s">
-        <v>9</v>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈칸의 개수 (COUNTBLANK 함수 사용)</t>
+        </is>
       </c>
       <c r="C10" s="13" t="s">
         <v>9</v>
@@ -707,10 +730,12 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="24.95" customHeight="1">
+    <row r="11" spans="1:12" ht="44" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="13" t="s">
-        <v>10</v>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫자의 개수 (COUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C11" s="13" t="s">
         <v>10</v>
@@ -720,8 +745,10 @@
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="3" t="s">
-        <v>11</v>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분산 (VAR.S 함수 사용)</t>
+        </is>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="1"/>
@@ -729,15 +756,17 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="24.95" customHeight="1">
+    <row r="12" spans="1:12" ht="44" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="3" t="s">
-        <v>12</v>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표준편차 (STDEV.S 함수 사용)</t>
+        </is>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="1"/>
@@ -745,15 +774,18 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="24.95" customHeight="1">
+    <row r="13" spans="1:12" ht="44" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2번째로 큰 값
+(LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="1"/>
@@ -761,15 +793,18 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="24.95" customHeight="1">
+    <row r="14" spans="1:12" ht="44" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3번째로 작은 값
+(SMALL 함수 사용)</t>
+        </is>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="1"/>
@@ -791,14 +826,19 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="24.95" customHeight="1">
+    <row r="16" spans="1:12" ht="44" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B17의 연도 4글자를 숫자로 추출
+(VALUE, MID 함수 사용)</t>
+        </is>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -901,10 +941,12 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" ht="24.95" customHeight="1">
+    <row r="22" spans="1:12" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="12" t="s">
-        <v>20</v>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 A, 수량 50 이상 개수 (COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="12" t="s">
         <v>20</v>
@@ -1065,7 +1107,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="24.95" customHeight="1">
+    <row r="31" spans="1:12" ht="44" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>100</v>
@@ -1076,8 +1118,10 @@
       <c r="D31" s="11"/>
       <c r="E31" s="6"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>28</v>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫자 개수 (COUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1085,7 +1129,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="24.95" customHeight="1">
+    <row r="32" spans="1:12" ht="44" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
         <v>29</v>
@@ -1096,8 +1140,11 @@
       <c r="D32" s="11"/>
       <c r="E32" s="6"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>31</v>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비어 있지 않은 개수
+(COUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1105,7 +1152,7 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:12" ht="24.95" customHeight="1">
+    <row r="33" spans="1:12" ht="44" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>0</v>
@@ -1116,8 +1163,10 @@
       <c r="D33" s="11"/>
       <c r="E33" s="6"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>33</v>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈칸 개수 (COUNTBLANK 함수 사용)</t>
+        </is>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1125,7 +1174,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" ht="24.95" customHeight="1">
+    <row r="34" spans="1:12" ht="44" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="11" t="s">
@@ -1134,8 +1183,11 @@
       <c r="D34" s="11"/>
       <c r="E34" s="6"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>35</v>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250점의 오름차순 등수
+(RANK.EQ 함수 사용)</t>
+        </is>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1143,7 +1195,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" ht="24.95" customHeight="1">
+    <row r="35" spans="1:12" ht="44" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>0</v>
@@ -1154,8 +1206,10 @@
       <c r="D35" s="11"/>
       <c r="E35" s="6"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>37</v>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가장 큰 총점 (LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1163,7 +1217,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" ht="24.95" customHeight="1">
+    <row r="36" spans="1:12" ht="44" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="str">
         <f>""</f>
@@ -1175,8 +1229,11 @@
       <c r="D36" s="11"/>
       <c r="E36" s="6"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>39</v>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">총점 350 이상 개수
+(COUNTIF 함수 사용)</t>
+        </is>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1184,15 +1241,18 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:12" ht="24.95" customHeight="1">
+    <row r="37" spans="1:12" ht="44" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="6"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>40</v>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 B, 수량 50 이상 개수
+(COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1200,15 +1260,18 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" ht="24.95" customHeight="1">
+    <row r="38" spans="1:12" ht="44" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="6"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>41</v>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 A, 수량 G27 이상 개수
+(COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1326,7 +1389,7 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="24.95" customHeight="1">
+    <row r="2" spans="1:12" ht="44" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2">
         <v>100</v>
@@ -1344,12 +1407,17 @@
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>2</v>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내림차순 등수
+(RANK.EQ 함수 사용)</t>
+        </is>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>43</v>
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노란색 셀에 지정된 함수로 수식을 입력하세요.</t>
+        </is>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1471,10 +1539,12 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="24.95" customHeight="1">
+    <row r="8" spans="1:12" ht="44" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="13" t="s">
-        <v>7</v>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울의 개수 (COUNTIF 함수 사용)</t>
+        </is>
       </c>
       <c r="C8" s="13" t="s">
         <v>7</v>
@@ -1499,10 +1569,12 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" ht="24.95" customHeight="1">
+    <row r="9" spans="1:12" ht="44" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="13" t="s">
-        <v>8</v>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비어 있지 않은 셀의 개수 (COUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="C9" s="13" t="s">
         <v>8</v>
@@ -1527,10 +1599,12 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" ht="24.95" customHeight="1">
+    <row r="10" spans="1:12" ht="44" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="13" t="s">
-        <v>9</v>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈칸의 개수 (COUNTBLANK 함수 사용)</t>
+        </is>
       </c>
       <c r="C10" s="13" t="s">
         <v>9</v>
@@ -1550,10 +1624,12 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="24.95" customHeight="1">
+    <row r="11" spans="1:12" ht="44" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="13" t="s">
-        <v>10</v>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫자의 개수 (COUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="C11" s="13" t="s">
         <v>10</v>
@@ -1566,8 +1642,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="3" t="s">
-        <v>11</v>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분산 (VAR.S 함수 사용)</t>
+        </is>
       </c>
       <c r="H11" s="9">
         <f>_xlfn.VAR.S(G3:G9)</f>
@@ -1578,15 +1656,17 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="24.95" customHeight="1">
+    <row r="12" spans="1:12" ht="44" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="3" t="s">
-        <v>12</v>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표준편차 (STDEV.S 함수 사용)</t>
+        </is>
       </c>
       <c r="H12" s="9">
         <f>_xlfn.STDEV.S(G3:G9)</f>
@@ -1597,15 +1677,18 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="24.95" customHeight="1">
+    <row r="13" spans="1:12" ht="44" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2번째로 큰 값
+(LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="H13" s="10">
         <f>LARGE(G3:G9,2)</f>
@@ -1616,15 +1699,18 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="24.95" customHeight="1">
+    <row r="14" spans="1:12" ht="44" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3번째로 작은 값
+(SMALL 함수 사용)</t>
+        </is>
       </c>
       <c r="H14" s="10">
         <f>SMALL(G3:G9,3)</f>
@@ -1649,14 +1735,19 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="24.95" customHeight="1">
+    <row r="16" spans="1:12" ht="44" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B17의 연도 4글자를 숫자로 추출
+(VALUE, MID 함수 사용)</t>
+        </is>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1762,10 +1853,12 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" ht="24.95" customHeight="1">
+    <row r="22" spans="1:12" ht="44" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="12" t="s">
-        <v>20</v>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 A, 수량 50 이상 개수 (COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="C22" s="12" t="s">
         <v>20</v>
@@ -1929,7 +2022,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:12" ht="24.95" customHeight="1">
+    <row r="31" spans="1:12" ht="44" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>100</v>
@@ -1943,8 +2036,10 @@
         <v>2</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>28</v>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫자 개수 (COUNT 함수 사용)</t>
+        </is>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1952,7 +2047,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="24.95" customHeight="1">
+    <row r="32" spans="1:12" ht="44" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
         <v>29</v>
@@ -1966,8 +2061,11 @@
         <v>5</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>31</v>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비어 있지 않은 개수
+(COUNTA 함수 사용)</t>
+        </is>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1975,7 +2073,7 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:12" ht="24.95" customHeight="1">
+    <row r="33" spans="1:12" ht="44" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>0</v>
@@ -1989,8 +2087,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>33</v>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈칸 개수 (COUNTBLANK 함수 사용)</t>
+        </is>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1998,7 +2098,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="1:12" ht="24.95" customHeight="1">
+    <row r="34" spans="1:12" ht="44" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="11" t="s">
@@ -2010,8 +2110,11 @@
         <v>1</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>35</v>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250점의 오름차순 등수
+(RANK.EQ 함수 사용)</t>
+        </is>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2019,7 +2122,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" ht="24.95" customHeight="1">
+    <row r="35" spans="1:12" ht="44" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
         <v>0</v>
@@ -2033,8 +2136,10 @@
         <v>600</v>
       </c>
       <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>37</v>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가장 큰 총점 (LARGE 함수 사용)</t>
+        </is>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2042,7 +2147,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" ht="24.95" customHeight="1">
+    <row r="36" spans="1:12" ht="44" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="str">
         <f>""</f>
@@ -2057,8 +2162,11 @@
         <v>5</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>39</v>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">총점 350 이상 개수
+(COUNTIF 함수 사용)</t>
+        </is>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2066,7 +2174,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:12" ht="24.95" customHeight="1">
+    <row r="37" spans="1:12" ht="44" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2076,8 +2184,11 @@
         <v>2</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>40</v>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 B, 수량 50 이상 개수
+(COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2085,7 +2196,7 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" ht="24.95" customHeight="1">
+    <row r="38" spans="1:12" ht="44" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2095,8 +2206,11 @@
         <v>2</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>41</v>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 A, 수량 G27 이상 개수
+(COUNTIFS 함수 사용)</t>
+        </is>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
